--- a/tools/test-harness/shots/quote-test.xlsx
+++ b/tools/test-harness/shots/quote-test.xlsx
@@ -713,13 +713,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7EBD88F-C7A0-4086-A9F4-C24B43F1AED7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C46C459E-E51E-45D6-9191-A8220DBF4D70}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E8C1B9C-2331-4D3D-AC6B-DB3FC050C224}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D165663-7A27-49CC-841C-196A1B831052}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1F7CC00-CA19-4AC9-A1FC-FECF6E6823E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715083FC-D611-406D-9E52-BD21721103C2}"/>
 </file>
--- a/tools/test-harness/shots/quote-test.xlsx
+++ b/tools/test-harness/shots/quote-test.xlsx
@@ -713,13 +713,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C46C459E-E51E-45D6-9191-A8220DBF4D70}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F907BF9-1F25-4124-B4E2-919004475572}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D165663-7A27-49CC-841C-196A1B831052}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5533348-2C7D-4A00-BC96-8D63E6281C2D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{715083FC-D611-406D-9E52-BD21721103C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EF4784C-0611-429C-B8D5-3B499037BD28}"/>
 </file>
--- a/tools/test-harness/shots/quote-test.xlsx
+++ b/tools/test-harness/shots/quote-test.xlsx
@@ -713,13 +713,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F907BF9-1F25-4124-B4E2-919004475572}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90F4ACD-74F4-4B25-9F12-7F65E463E77D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5533348-2C7D-4A00-BC96-8D63E6281C2D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A87C543B-4503-43F8-9092-0E7E582FBDBD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EF4784C-0611-429C-B8D5-3B499037BD28}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F09371D4-2546-4B88-82B3-60797FACBEA7}"/>
 </file>
--- a/tools/test-harness/shots/quote-test.xlsx
+++ b/tools/test-harness/shots/quote-test.xlsx
@@ -713,13 +713,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C90F4ACD-74F4-4B25-9F12-7F65E463E77D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06FB809-CE3F-4C44-BB40-9C1E05274929}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A87C543B-4503-43F8-9092-0E7E582FBDBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1291FA33-F731-4F0D-A6D1-822D166A69BF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F09371D4-2546-4B88-82B3-60797FACBEA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C9FF0B6-4C1F-47DA-9091-6DA1D1603847}"/>
 </file>